--- a/data/single_sentence_hate_speech_labeled_samples.xlsx
+++ b/data/single_sentence_hate_speech_labeled_samples.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdodovic\Desktop\LLM-HS-Detector\HateSpeech-LLM-Detector\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3846C4F3-7E22-4DAE-A1B1-FA253A98FC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1AD45D-48E8-492C-871E-D0DD307CCF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="2895" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="19440" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Labels" sheetId="1" r:id="rId1"/>
@@ -48,51 +48,6 @@
     <t>Category</t>
   </si>
   <si>
-    <t>1. Uvek se najvise zarađuje na nekvalitetu.</t>
-  </si>
-  <si>
-    <t>3. Istopolni brakovi su nonsens, uteha za učesnike.</t>
-  </si>
-  <si>
-    <t>4. Danas ako hoćeš poziciju da imaš ili kurva da si peder ili lezbejka.</t>
-  </si>
-  <si>
-    <t>5. Neki od Vučićevih štakora će možda da se izvuku. Ali ona će zažaliti dan kada ga je upoznala. A tužno je nesvesna te činjenice.</t>
-  </si>
-  <si>
-    <t>6. Evo zašto. Ujutro kad ustaneš, na odmoran mozak poslušaj dok si sama, pa možda i shvatiš. Niko ne reaguje jer nikog nije ni uvredio sem vas koji živite u ružičastom balonu.</t>
-  </si>
-  <si>
-    <t>7. Ne poznajem nijednog vlasnika pit bula ili staforda,ciji je pas napao nekoga,a da ta osoba nije bila kompletan agresivni idiot i uglavnom bilder.</t>
-  </si>
-  <si>
-    <t>8. Mene sramota što sam Srbin kad slušam ovog, ne znam kako da ga nazovem!! On zajebava ovaj narod i treba da ga uništava kad je parizer brend!! Novak Đoković kad dođe da se nominuje onda ću da glasam jer ovo su ljudski odron!</t>
-  </si>
-  <si>
-    <t>10. Ovaj Momirović je jedan od žešćih imbecila koji su bili u vlasti. Vređa inteligenciju!</t>
-  </si>
-  <si>
-    <t>12. Ja sam mislio da mi u Hrvatskoj imamo bolesnike,ali vi u Srbiji ste nas nadjebali.</t>
-  </si>
-  <si>
-    <t>14. I on je sam svestan da mu je glava prazna...šuplja.To je opasna stvar.Ovaj kad pogreši...a to radi svakodnevno,on pravi nepopravljivu katastrofu.Kad ovakav tupan-glupan glumi 'stručnjaka' pa to je tempirana bomba.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. Kako sam srećan kada gledam ovog mladog ministra tako uliva nadu i nama koji nismo završili nikakve škole da možemo jednog dana upravljati državom.❤ </t>
-  </si>
-  <si>
-    <t>16. Samo nepismen narod trpi ovakve smradove i ljigavce. Ne krivim više njih već narod koji ih bira.... Narod kom je Zadruga glavni vid zabave, a omladina sa dve moždane ćelije, ne može da se nada ničem dobrom nažalost. Stid me Srpstva zbog Vučića i ovih degenerika oko njega.</t>
-  </si>
-  <si>
-    <t>17. 36 artikala, 36 dis prodavnica, i posle pređenih 360km je kupljeno na akciji sve kvalitetno.</t>
-  </si>
-  <si>
-    <t>19. Ovako izgleda kada je novinar gospodin i profesionalno radi intervju, za normalnog dosta, nema potrebe za rešetanjem, pozivanjem, preskanjem, sve je objasnio pitanjima i  komentarima na odgovore. Svako iole normalan je razumeo osim konzumatora pinka i parizera.</t>
-  </si>
-  <si>
-    <t>20. Razlika između "PARIZERA" i mortadelle je otprilike, kao što je razlika između Trabanta i Audija....😅</t>
-  </si>
-  <si>
     <t>3b</t>
   </si>
   <si>
@@ -103,6 +58,51 @@
   </si>
   <si>
     <t>1c</t>
+  </si>
+  <si>
+    <t>Uvek se najvise zarađuje na nekvalitetu.</t>
+  </si>
+  <si>
+    <t>Istopolni brakovi su nonsens, uteha za učesnike.</t>
+  </si>
+  <si>
+    <t>Danas ako hoćeš poziciju da imaš ili kurva da si peder ili lezbejka.</t>
+  </si>
+  <si>
+    <t>Ne poznajem nijednog vlasnika pit bula ili staforda,ciji je pas napao nekoga,a da ta osoba nije bila kompletan agresivni idiot i uglavnom bilder.</t>
+  </si>
+  <si>
+    <t>Ja sam mislio da mi u Hrvatskoj imamo bolesnike,ali vi u Srbiji ste nas nadjebali.</t>
+  </si>
+  <si>
+    <t>36 artikala, 36 dis prodavnica, i posle pređenih 360km je kupljeno na akciji sve kvalitetno.</t>
+  </si>
+  <si>
+    <t>Neki od Vučićevih štakora će možda da se izvuku, ali ona će zažaliti dan kada ga je upoznala, a tužno je nesvesna te činjenice.</t>
+  </si>
+  <si>
+    <t>Razlika između "PARIZERA" i mortadelle je otprilike, kao što je razlika između Trabanta i Audija.</t>
+  </si>
+  <si>
+    <t>Ovako izgleda kada je novinar gospodin i profesionalno radi intervju, za normalnog dosta, nema potrebe za rešetanjem, pozivanjem, preskanjem, sve je objasnio pitanjima i  komentarima na odgovore,a svako iole normalan je razumeo osim konzumatora pinka i parizera.</t>
+  </si>
+  <si>
+    <t>Samo nepismen narod trpi ovakve smradove i ljigavce, ne krivim više njih već narod koji ih bira, narod kom je Zadruga glavni vid zabave, a omladina sa dve moždane ćelije, ne može da se nada ničem dobrom nažalost, stid me Srpstva zbog Vučića i ovih degenerika oko njega.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kako sam srećan kada gledam ovog mladog ministra tako uliva nadu i nama koji nismo završili nikakve škole da možemo jednog dana upravljati državom. </t>
+  </si>
+  <si>
+    <t>I on je sam svestan da mu je glava prazna, šuplja, to je opasna stvar, kad pogreši, a to radi svakodnevno,on pravi nepopravljivu katastrofu, kad ovakav tupan-glupan glumi 'stručnjaka' pa to je tempirana bomba.</t>
+  </si>
+  <si>
+    <t>Ovaj Momirović je jedan od žešćih imbecila koji su bili u vlasti, vređa inteligenciju!</t>
+  </si>
+  <si>
+    <t>Mene sramota što sam Srbin kad slušam ovog, ne znam kako da ga nazovem, on zajebava ovaj narod i treba da ga uništava kad je parizer brend, Novak Đoković kad dođe da se nominuje onda ću da glasam jer ovo su ljudski odron!</t>
+  </si>
+  <si>
+    <t>Evo zašto,ujutro kad ustaneš, na odmoran mozak poslušaj dok si sama, pa možda i shvatiš, niko ne reaguje jer nikog nije ni uvredio sem vas koji živite u ružičastom balonu.</t>
   </si>
 </sst>
 </file>
@@ -427,7 +427,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6">
         <v>0</v>
@@ -438,10 +438,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -449,10 +449,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -460,10 +460,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -471,7 +471,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C6" s="6">
         <v>0</v>
@@ -482,10 +482,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -493,10 +493,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -504,10 +504,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -518,7 +518,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -526,10 +526,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -537,7 +537,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" s="6">
         <v>0</v>
@@ -548,10 +548,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -559,7 +559,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" s="6">
         <v>0</v>
@@ -570,7 +570,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="6">
         <v>0</v>
@@ -581,7 +581,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" s="6">
         <v>0</v>
